--- a/Agile project tracking/Defect_Tracker Template_v0.1.xlsx
+++ b/Agile project tracking/Defect_Tracker Template_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumba\Desktop\tracker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumba\Desktop\CRSA-Agent\Agile project tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA0C406-B032-4966-8FB9-413D0279954B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F5902C-29B7-436C-8DDF-6C6DB316B5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,23 @@
     <sheet name="Defects" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>Sl No</t>
   </si>
@@ -97,6 +108,36 @@
   </si>
   <si>
     <t>Problem with offical Google Model</t>
+  </si>
+  <si>
+    <t>Code Analysis Agent was not identifying code-quality issues such as code smells, excessive complexity, and poor coding practices consistently.</t>
+  </si>
+  <si>
+    <t>Developed the Code Analysis Agent to identify code-quality issues and return structured findings with severity classifications and recommendations.</t>
+  </si>
+  <si>
+    <t>Further testing is required to validate detection accuracy across Python and Java samples.</t>
+  </si>
+  <si>
+    <t>Security Analysis Agent required a structured approach to detecting vulnerabilities and classifying their severity.</t>
+  </si>
+  <si>
+    <t>Implemented the security analysis workflow to identify common vulnerabilities, provide severity levels, and generate remediation recommendations.</t>
+  </si>
+  <si>
+    <t>Validate vulnerability detection against different security test cases.</t>
+  </si>
+  <si>
+    <t>Findings from the Code Analysis and Security Analysis agents needed to be integrated into a unified LangGraph workflow.</t>
+  </si>
+  <si>
+    <t>Worked on parallel execution of both agents and merging their outputs into a unified findings list for the final code-review report.</t>
+  </si>
+  <si>
+    <t>End-to-end integration and result consistency testing are pending.</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
   </si>
 </sst>
 </file>
@@ -655,44 +696,98 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C4" s="8">
+        <v>46316</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="8">
+        <v>46316</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C5" s="8">
+        <v>46321</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="8">
+        <v>46321</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="C6" s="8">
+        <v>46322</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="8">
+        <v>46322</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
@@ -888,7 +983,7 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>G1:G1048576</xm:sqref>
+          <xm:sqref>G1:G5 G7:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -933,12 +1028,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1074,15 +1166,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1106,10 +1202,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>